--- a/artfynd/A 38898-2024 artfynd.xlsx
+++ b/artfynd/A 38898-2024 artfynd.xlsx
@@ -803,14 +803,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119720111</v>
+        <v>119720114</v>
       </c>
       <c r="B3" t="n">
-        <v>57329</v>
+        <v>94574</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -819,46 +819,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Utkiksberget, Utkiksberget, Srm</t>
+          <t>Utkiksberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598847</v>
+        <v>598862</v>
       </c>
       <c r="R3" t="n">
-        <v>6535001</v>
+        <v>6535067</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -890,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,14 +919,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119720114</v>
+        <v>119720115</v>
       </c>
       <c r="B4" t="n">
-        <v>94574</v>
+        <v>94681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -943,38 +935,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Utkiksberget, Srm</t>
+          <t>Utkiksberget, Utkiksberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598862</v>
+        <v>598859</v>
       </c>
       <c r="R4" t="n">
-        <v>6535067</v>
+        <v>6535024</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1006,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119720115</v>
+        <v>119720111</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>57329</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,31 +1055,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598859</v>
+        <v>598847</v>
       </c>
       <c r="R5" t="n">
-        <v>6535024</v>
+        <v>6535001</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 38898-2024 artfynd.xlsx
+++ b/artfynd/A 38898-2024 artfynd.xlsx
@@ -803,14 +803,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119720114</v>
+        <v>119720111</v>
       </c>
       <c r="B3" t="n">
-        <v>94574</v>
+        <v>57339</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -819,38 +819,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Utkiksberget, Srm</t>
+          <t>Utkiksberget, Utkiksberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598862</v>
+        <v>598847</v>
       </c>
       <c r="R3" t="n">
-        <v>6535067</v>
+        <v>6535001</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -882,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,14 +927,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119720115</v>
+        <v>119720114</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>94597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,42 +943,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Utkiksberget, Utkiksberget, Srm</t>
+          <t>Utkiksberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598859</v>
+        <v>598862</v>
       </c>
       <c r="R4" t="n">
-        <v>6535024</v>
+        <v>6535067</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1002,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119720111</v>
+        <v>119720115</v>
       </c>
       <c r="B5" t="n">
-        <v>57329</v>
+        <v>94704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,35 +1059,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598847</v>
+        <v>598859</v>
       </c>
       <c r="R5" t="n">
-        <v>6535001</v>
+        <v>6535024</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
